--- a/src/cubes/data/housing_stock/air-infiltration.xlsx
+++ b/src/cubes/data/housing_stock/air-infiltration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/housing_stock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ACF94B-E494-C94E-B99E-56A4DBB12370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99465647-EDFD-0F44-AE5A-9D589792BD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20720" windowHeight="21100" xr2:uid="{A87ED9AA-C9BB-DB4B-8FB0-476C7592F5D5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{A87ED9AA-C9BB-DB4B-8FB0-476C7592F5D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
   <si>
     <t>Paper</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>Alo Mikola, Targo Kalamees, Teet-Andrus Kõiv</t>
+  </si>
+  <si>
+    <t>MERGE INTEGER</t>
   </si>
 </sst>
 </file>
@@ -461,18 +464,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A9008ED-63AB-CD4F-9BBD-3132D8B71A8F}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.6640625" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="42.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2">
         <v>2</v>
@@ -492,7 +495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -503,7 +506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4">
         <v>2</v>
@@ -512,7 +515,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -523,7 +526,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6">
         <v>2</v>
@@ -532,7 +535,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -543,7 +546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2</v>
       </c>
@@ -551,7 +554,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -559,19 +562,22 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -579,19 +585,22 @@
         <v>8</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>1950</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>1966</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>7.88</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.1484</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2</v>
       </c>
@@ -599,19 +608,22 @@
         <v>6</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>1996</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>2002</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>6.03</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.20930000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -619,19 +631,22 @@
         <v>8</v>
       </c>
       <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
         <v>1850</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>1900</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>7.9</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.20799999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>4</v>
       </c>
@@ -639,19 +654,22 @@
         <v>6</v>
       </c>
       <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
         <v>2003</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>2006</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.1241</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5</v>
       </c>
@@ -659,19 +677,22 @@
         <v>8</v>
       </c>
       <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
         <v>1976</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>1982</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>3.86</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>7.8700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>6</v>
       </c>
@@ -679,19 +700,22 @@
         <v>6</v>
       </c>
       <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
         <v>1950</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>1966</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>7.6</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.31709999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>7</v>
       </c>
@@ -699,19 +723,22 @@
         <v>7</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>1900</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1929</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>7.22</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.35120000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>8</v>
       </c>
@@ -719,19 +746,22 @@
         <v>6</v>
       </c>
       <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
         <v>1996</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>2002</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>6.04</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.16450000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>9</v>
       </c>
@@ -739,19 +769,22 @@
         <v>7</v>
       </c>
       <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
         <v>1976</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>1982</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>6.81</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.15140000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>10</v>
       </c>
@@ -759,19 +792,22 @@
         <v>7</v>
       </c>
       <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
         <v>1983</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>1990</v>
       </c>
-      <c r="E20" s="2">
+      <c r="F20" s="2">
         <v>10.039999999999999</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.2344</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>11</v>
       </c>
@@ -779,19 +815,22 @@
         <v>7</v>
       </c>
       <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
         <v>1991</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>1995</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>8.77</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.22839999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>12</v>
       </c>
@@ -799,19 +838,22 @@
         <v>6</v>
       </c>
       <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22">
         <v>2003</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>2006</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>5.85</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.25330000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>13</v>
       </c>
@@ -819,19 +861,22 @@
         <v>6</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
         <v>1900</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>1929</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="2">
         <v>13.61</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.41920000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>14</v>
       </c>
@@ -839,19 +884,22 @@
         <v>6</v>
       </c>
       <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24">
         <v>1991</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>1995</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="2">
         <v>4.68</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>8.4900000000000003E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>15</v>
       </c>
@@ -859,19 +907,22 @@
         <v>8</v>
       </c>
       <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
         <v>2012</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>2023</v>
       </c>
-      <c r="E25" s="2">
+      <c r="F25" s="2">
         <v>5.33</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.15040000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>16</v>
       </c>
@@ -879,19 +930,22 @@
         <v>7</v>
       </c>
       <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
         <v>1991</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>1995</v>
       </c>
-      <c r="E26" s="2">
+      <c r="F26" s="2">
         <v>11.16</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.51890000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>17</v>
       </c>
@@ -899,19 +953,22 @@
         <v>8</v>
       </c>
       <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
         <v>2012</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>2023</v>
       </c>
-      <c r="E27" s="2">
+      <c r="F27" s="2">
         <v>4.29</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>9.98E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>18</v>
       </c>
@@ -919,19 +976,22 @@
         <v>7</v>
       </c>
       <c r="C28">
+        <v>6</v>
+      </c>
+      <c r="D28">
         <v>1930</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>1949</v>
       </c>
-      <c r="E28" s="2">
+      <c r="F28" s="2">
         <v>9.92</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.3594</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>19</v>
       </c>
@@ -939,19 +999,22 @@
         <v>8</v>
       </c>
       <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
         <v>1983</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>1990</v>
       </c>
-      <c r="E29" s="2">
+      <c r="F29" s="2">
         <v>13.43</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.2928</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>20</v>
       </c>
@@ -959,19 +1022,22 @@
         <v>8</v>
       </c>
       <c r="C30">
+        <v>7</v>
+      </c>
+      <c r="D30">
         <v>1950</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>1966</v>
       </c>
-      <c r="E30" s="2">
+      <c r="F30" s="2">
         <v>13.87</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.27529999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>21</v>
       </c>
@@ -979,47 +1045,57 @@
         <v>8</v>
       </c>
       <c r="C31">
+        <v>8</v>
+      </c>
+      <c r="D31">
         <v>2003</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>2006</v>
       </c>
-      <c r="E31" s="2">
+      <c r="F31" s="2">
         <v>7.6</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.36180000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
         <v>2000</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>2023</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>0.42</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
         <v>1850</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>0.24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/src/cubes/data/housing_stock/air-infiltration.xlsx
+++ b/src/cubes/data/housing_stock/air-infiltration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/housing_stock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99465647-EDFD-0F44-AE5A-9D589792BD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28BAB5-0A4F-7C45-B3A9-24290F33EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{A87ED9AA-C9BB-DB4B-8FB0-476C7592F5D5}"/>
+    <workbookView xWindow="380" yWindow="1320" windowWidth="30240" windowHeight="18880" xr2:uid="{A87ED9AA-C9BB-DB4B-8FB0-476C7592F5D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -106,7 +106,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/src/cubes/data/housing_stock/air-infiltration.xlsx
+++ b/src/cubes/data/housing_stock/air-infiltration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/housing_stock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B28BAB5-0A4F-7C45-B3A9-24290F33EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE23D52A-BEA3-BD4C-9B36-982B69E4BA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="1320" windowWidth="30240" windowHeight="18880" xr2:uid="{A87ED9AA-C9BB-DB4B-8FB0-476C7592F5D5}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>REFERENCE BUILDING AIR PERMEABILITY</t>
   </si>
   <si>
-    <t>REFERENCE BUILDING AIR INFILTRATION</t>
-  </si>
-  <si>
     <t>ABL</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t>MERGE INTEGER</t>
+  </si>
+  <si>
+    <t>AIR INFILTRATION</t>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -512,7 +512,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -551,7 +551,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -562,7 +562,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>11</v>
@@ -574,7 +574,7 @@
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1062,7 +1062,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33">
         <v>2</v>
